--- a/artfynd/A 47898-2022 artfynd.xlsx
+++ b/artfynd/A 47898-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47898-2022 artfynd.xlsx
+++ b/artfynd/A 47898-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6767088</v>
+        <v>6759761</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694769.8227426508</v>
+        <v>694770</v>
       </c>
       <c r="R2" t="n">
-        <v>6672506.047464129</v>
+        <v>6672506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,27 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-05-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>32 ex (med 12 blommor)</t>
+          <t>2006-05-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,6 +787,583 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>417156</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101947</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hällebräcka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saxifraga osloënsis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lavarö, 500 m NV om, intill järnvägen (*hällebräcka* /plant/), Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>694741</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6672499</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>AB-Nor-0238</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1995-06-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1995-06-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>12J4a. Lokalen tidigare angiven med 6672400 1650115 100 m hällar och klippkant i järnvägsskärning, banvall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>klippkant i järnvägsskärning</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>AB-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>426299</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hällebräcka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Saxifraga osloënsis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Edebo Lavarö, 500 m NV-ut, N järnvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694799</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6672458</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2006-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2006-05-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>flacka hällar</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri AB-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>426300</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hällebräcka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Saxifraga osloënsis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Edebo Lavarö, 500 m NV-ut, S järnvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>694791</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6672465</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2006-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2006-05-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>banvall</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri AB-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118595548</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lavarö, NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>694764</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6672497</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På väddklint</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linda Irebrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linda Irebrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118595537</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lavarö, NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>694764</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6672497</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid vägkant.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda Irebrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda Irebrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47898-2022 artfynd.xlsx
+++ b/artfynd/A 47898-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759761</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/417156</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/426299</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/426300</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118595548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,8 +1394,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118595537</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>